--- a/杂项 misc/比较器信号.xlsx
+++ b/杂项 misc/比较器信号.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Minecraft\tree-hole\杂项 misc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD6115D-38D6-45E4-A8E8-A06A69ECACE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD4DE240-3C09-4855-AAE6-F840299C1FF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="244">
   <si>
     <t>容器</t>
   </si>
@@ -1459,6 +1459,57 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="34" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="36" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="37" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="38" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1471,18 +1522,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1494,45 +1533,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="34" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="36" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2118,7 +2118,7 @@
       <c r="B2" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="77"/>
+      <c r="C2" s="82"/>
       <c r="D2" s="34" t="s">
         <v>25</v>
       </c>
@@ -2137,75 +2137,75 @@
       <c r="I2" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="92" t="s">
+      <c r="J2" s="77" t="s">
         <v>27</v>
       </c>
       <c r="K2" s="44" t="s">
         <v>215</v>
       </c>
-      <c r="L2" s="84" t="s">
+      <c r="L2" s="72" t="s">
         <v>217</v>
       </c>
-      <c r="M2" s="84"/>
-      <c r="N2" s="84"/>
-      <c r="O2" s="79" t="s">
+      <c r="M2" s="72"/>
+      <c r="N2" s="72"/>
+      <c r="O2" s="84" t="s">
         <v>205</v>
       </c>
       <c r="P2" s="85" t="s">
         <v>243</v>
       </c>
-      <c r="Q2" s="77" t="s">
+      <c r="Q2" s="82" t="s">
         <v>242</v>
       </c>
-      <c r="R2" s="79" t="s">
+      <c r="R2" s="84" t="s">
         <v>201</v>
       </c>
-      <c r="S2" s="78"/>
+      <c r="S2" s="83"/>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="32">
         <v>1</v>
       </c>
-      <c r="B3" s="76"/>
-      <c r="C3" s="77"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="82"/>
       <c r="D3" s="39" t="s">
         <v>28</v>
       </c>
       <c r="E3" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="77"/>
+      <c r="F3" s="82"/>
       <c r="G3" s="41" t="s">
         <v>30</v>
       </c>
       <c r="H3" s="41" t="s">
         <v>232</v>
       </c>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
-      <c r="K3" s="88">
+      <c r="I3" s="82"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="73">
         <v>1</v>
       </c>
-      <c r="L3" s="90">
+      <c r="L3" s="75">
         <v>1</v>
       </c>
-      <c r="M3" s="95" t="s">
+      <c r="M3" s="80" t="s">
         <v>225</v>
       </c>
-      <c r="N3" s="93" t="s">
+      <c r="N3" s="78" t="s">
         <v>226</v>
       </c>
-      <c r="O3" s="79"/>
+      <c r="O3" s="84"/>
       <c r="P3" s="86"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="79"/>
-      <c r="S3" s="78"/>
+      <c r="Q3" s="82"/>
+      <c r="R3" s="84"/>
+      <c r="S3" s="83"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="32">
         <v>2</v>
       </c>
-      <c r="B4" s="76"/>
+      <c r="B4" s="88"/>
       <c r="C4" s="36" t="s">
         <v>31</v>
       </c>
@@ -2215,32 +2215,32 @@
       <c r="E4" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="77"/>
+      <c r="F4" s="82"/>
       <c r="G4" s="41" t="s">
         <v>34</v>
       </c>
       <c r="H4" s="41" t="s">
         <v>233</v>
       </c>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
-      <c r="K4" s="88">
+      <c r="I4" s="82"/>
+      <c r="J4" s="82"/>
+      <c r="K4" s="73">
         <v>2</v>
       </c>
-      <c r="L4" s="90">
+      <c r="L4" s="75">
         <v>2</v>
       </c>
-      <c r="M4" s="95" t="s">
+      <c r="M4" s="80" t="s">
         <v>224</v>
       </c>
-      <c r="N4" s="90" t="s">
+      <c r="N4" s="75" t="s">
         <v>227</v>
       </c>
-      <c r="O4" s="79"/>
+      <c r="O4" s="84"/>
       <c r="P4" s="86"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="79"/>
-      <c r="S4" s="78"/>
+      <c r="Q4" s="82"/>
+      <c r="R4" s="84"/>
+      <c r="S4" s="83"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="32">
@@ -2265,136 +2265,136 @@
       <c r="H5" s="41" t="s">
         <v>234</v>
       </c>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
-      <c r="K5" s="88">
+      <c r="I5" s="82"/>
+      <c r="J5" s="82"/>
+      <c r="K5" s="73">
         <v>3</v>
       </c>
-      <c r="L5" s="90">
+      <c r="L5" s="75">
         <v>3</v>
       </c>
-      <c r="M5" s="95" t="s">
+      <c r="M5" s="80" t="s">
         <v>223</v>
       </c>
-      <c r="N5" s="91" t="s">
+      <c r="N5" s="76" t="s">
         <v>228</v>
       </c>
-      <c r="O5" s="79"/>
+      <c r="O5" s="84"/>
       <c r="P5" s="86"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="79"/>
-      <c r="S5" s="78"/>
+      <c r="Q5" s="82"/>
+      <c r="R5" s="84"/>
+      <c r="S5" s="83"/>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" s="19">
         <v>4</v>
       </c>
-      <c r="B6" s="76"/>
+      <c r="B6" s="88"/>
       <c r="C6" s="36" t="s">
         <v>40</v>
       </c>
       <c r="D6" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
+      <c r="E6" s="82"/>
+      <c r="F6" s="82"/>
       <c r="G6" s="41" t="s">
         <v>42</v>
       </c>
       <c r="H6" s="41" t="s">
         <v>235</v>
       </c>
-      <c r="I6" s="77"/>
-      <c r="J6" s="77"/>
+      <c r="I6" s="82"/>
+      <c r="J6" s="82"/>
       <c r="K6" s="38">
         <v>4</v>
       </c>
-      <c r="L6" s="91">
+      <c r="L6" s="76">
         <v>4</v>
       </c>
-      <c r="M6" s="96" t="s">
+      <c r="M6" s="81" t="s">
         <v>222</v>
       </c>
-      <c r="N6" s="94" t="s">
+      <c r="N6" s="79" t="s">
         <v>229</v>
       </c>
-      <c r="O6" s="79"/>
+      <c r="O6" s="84"/>
       <c r="P6" s="86"/>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="78"/>
+      <c r="Q6" s="82"/>
+      <c r="R6" s="84"/>
+      <c r="S6" s="83"/>
     </row>
     <row r="7" spans="1:19">
       <c r="A7" s="19">
         <v>5</v>
       </c>
-      <c r="B7" s="76"/>
+      <c r="B7" s="88"/>
       <c r="C7" s="44"/>
       <c r="D7" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="77"/>
-      <c r="F7" s="77"/>
+      <c r="E7" s="82"/>
+      <c r="F7" s="82"/>
       <c r="G7" s="48" t="s">
         <v>44</v>
       </c>
       <c r="H7" s="41" t="s">
         <v>236</v>
       </c>
-      <c r="I7" s="77"/>
-      <c r="J7" s="77"/>
+      <c r="I7" s="82"/>
+      <c r="J7" s="82"/>
       <c r="K7" s="38">
         <v>5</v>
       </c>
-      <c r="L7" s="91">
+      <c r="L7" s="76">
         <v>5</v>
       </c>
-      <c r="M7" s="96" t="s">
+      <c r="M7" s="81" t="s">
         <v>221</v>
       </c>
       <c r="N7" s="85" t="s">
         <v>230</v>
       </c>
-      <c r="O7" s="79"/>
+      <c r="O7" s="84"/>
       <c r="P7" s="86"/>
-      <c r="Q7" s="77"/>
-      <c r="R7" s="79"/>
-      <c r="S7" s="78"/>
+      <c r="Q7" s="82"/>
+      <c r="R7" s="84"/>
+      <c r="S7" s="83"/>
     </row>
     <row r="8" spans="1:19">
       <c r="A8" s="20">
         <v>6</v>
       </c>
-      <c r="B8" s="76"/>
+      <c r="B8" s="88"/>
       <c r="C8" s="41" t="s">
         <v>45</v>
       </c>
       <c r="D8" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="77"/>
-      <c r="F8" s="77"/>
-      <c r="G8" s="77"/>
+      <c r="E8" s="82"/>
+      <c r="F8" s="82"/>
+      <c r="G8" s="82"/>
       <c r="H8" s="41" t="s">
         <v>237</v>
       </c>
-      <c r="I8" s="77"/>
-      <c r="J8" s="77"/>
+      <c r="I8" s="82"/>
+      <c r="J8" s="82"/>
       <c r="K8" s="38">
         <v>6</v>
       </c>
-      <c r="L8" s="91">
+      <c r="L8" s="76">
         <v>6</v>
       </c>
-      <c r="M8" s="96" t="s">
+      <c r="M8" s="81" t="s">
         <v>220</v>
       </c>
       <c r="N8" s="86"/>
-      <c r="O8" s="79"/>
+      <c r="O8" s="84"/>
       <c r="P8" s="86"/>
-      <c r="Q8" s="77"/>
-      <c r="R8" s="79"/>
-      <c r="S8" s="78"/>
+      <c r="Q8" s="82"/>
+      <c r="R8" s="84"/>
+      <c r="S8" s="83"/>
     </row>
     <row r="9" spans="1:19">
       <c r="A9" s="20">
@@ -2407,50 +2407,50 @@
       <c r="D9" s="49" t="s">
         <v>48</v>
       </c>
-      <c r="E9" s="77"/>
-      <c r="F9" s="77"/>
-      <c r="G9" s="77"/>
+      <c r="E9" s="82"/>
+      <c r="F9" s="82"/>
+      <c r="G9" s="82"/>
       <c r="H9" s="41" t="s">
         <v>238</v>
       </c>
-      <c r="I9" s="77"/>
-      <c r="J9" s="77"/>
-      <c r="K9" s="89">
+      <c r="I9" s="82"/>
+      <c r="J9" s="82"/>
+      <c r="K9" s="74">
         <v>7</v>
       </c>
       <c r="L9" s="85" t="s">
         <v>218</v>
       </c>
-      <c r="M9" s="96" t="s">
+      <c r="M9" s="81" t="s">
         <v>219</v>
       </c>
       <c r="N9" s="86"/>
-      <c r="O9" s="79"/>
+      <c r="O9" s="84"/>
       <c r="P9" s="86"/>
-      <c r="Q9" s="77"/>
-      <c r="R9" s="79"/>
-      <c r="S9" s="78"/>
+      <c r="Q9" s="82"/>
+      <c r="R9" s="84"/>
+      <c r="S9" s="83"/>
     </row>
     <row r="10" spans="1:19">
       <c r="A10" s="21">
         <v>8</v>
       </c>
-      <c r="B10" s="76"/>
+      <c r="B10" s="88"/>
       <c r="C10" s="41" t="s">
         <v>49</v>
       </c>
       <c r="D10" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="77"/>
-      <c r="F10" s="77"/>
-      <c r="G10" s="77"/>
+      <c r="E10" s="82"/>
+      <c r="F10" s="82"/>
+      <c r="G10" s="82"/>
       <c r="H10" s="41" t="s">
         <v>239</v>
       </c>
-      <c r="I10" s="77"/>
-      <c r="J10" s="77"/>
-      <c r="K10" s="89">
+      <c r="I10" s="82"/>
+      <c r="J10" s="82"/>
+      <c r="K10" s="74">
         <v>8</v>
       </c>
       <c r="L10" s="86"/>
@@ -2458,65 +2458,65 @@
         <v>202</v>
       </c>
       <c r="N10" s="86"/>
-      <c r="O10" s="79"/>
+      <c r="O10" s="84"/>
       <c r="P10" s="86"/>
-      <c r="Q10" s="77"/>
-      <c r="R10" s="79"/>
-      <c r="S10" s="78"/>
+      <c r="Q10" s="82"/>
+      <c r="R10" s="84"/>
+      <c r="S10" s="83"/>
     </row>
     <row r="11" spans="1:19">
       <c r="A11" s="22">
         <v>9</v>
       </c>
-      <c r="B11" s="76"/>
+      <c r="B11" s="88"/>
       <c r="C11" s="44"/>
-      <c r="D11" s="77"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="77"/>
-      <c r="G11" s="77"/>
-      <c r="H11" s="77" t="s">
+      <c r="D11" s="82"/>
+      <c r="E11" s="82"/>
+      <c r="F11" s="82"/>
+      <c r="G11" s="82"/>
+      <c r="H11" s="82" t="s">
         <v>240</v>
       </c>
-      <c r="I11" s="77"/>
-      <c r="J11" s="77"/>
-      <c r="K11" s="89">
+      <c r="I11" s="82"/>
+      <c r="J11" s="82"/>
+      <c r="K11" s="74">
         <v>9</v>
       </c>
       <c r="L11" s="86"/>
       <c r="M11" s="86"/>
       <c r="N11" s="86"/>
-      <c r="O11" s="79"/>
+      <c r="O11" s="84"/>
       <c r="P11" s="86"/>
-      <c r="Q11" s="77"/>
-      <c r="R11" s="79"/>
-      <c r="S11" s="78"/>
+      <c r="Q11" s="82"/>
+      <c r="R11" s="84"/>
+      <c r="S11" s="83"/>
     </row>
     <row r="12" spans="1:19">
       <c r="A12" s="22">
         <v>10</v>
       </c>
-      <c r="B12" s="76"/>
+      <c r="B12" s="88"/>
       <c r="C12" s="50" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="77"/>
-      <c r="E12" s="77"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="77"/>
-      <c r="I12" s="77"/>
-      <c r="J12" s="77"/>
+      <c r="D12" s="82"/>
+      <c r="E12" s="82"/>
+      <c r="F12" s="82"/>
+      <c r="G12" s="82"/>
+      <c r="H12" s="82"/>
+      <c r="I12" s="82"/>
+      <c r="J12" s="82"/>
       <c r="K12" s="85" t="s">
         <v>216</v>
       </c>
       <c r="L12" s="86"/>
       <c r="M12" s="86"/>
       <c r="N12" s="86"/>
-      <c r="O12" s="79"/>
+      <c r="O12" s="84"/>
       <c r="P12" s="86"/>
-      <c r="Q12" s="77"/>
-      <c r="R12" s="79"/>
-      <c r="S12" s="78"/>
+      <c r="Q12" s="82"/>
+      <c r="R12" s="84"/>
+      <c r="S12" s="83"/>
     </row>
     <row r="13" spans="1:19">
       <c r="A13" s="23">
@@ -2526,95 +2526,95 @@
         <v>52</v>
       </c>
       <c r="C13" s="44"/>
-      <c r="D13" s="77"/>
-      <c r="E13" s="77"/>
-      <c r="F13" s="77"/>
-      <c r="G13" s="77"/>
-      <c r="H13" s="77"/>
-      <c r="I13" s="77"/>
-      <c r="J13" s="77"/>
+      <c r="D13" s="82"/>
+      <c r="E13" s="82"/>
+      <c r="F13" s="82"/>
+      <c r="G13" s="82"/>
+      <c r="H13" s="82"/>
+      <c r="I13" s="82"/>
+      <c r="J13" s="82"/>
       <c r="K13" s="86"/>
       <c r="L13" s="86"/>
       <c r="M13" s="86"/>
       <c r="N13" s="86"/>
-      <c r="O13" s="79"/>
+      <c r="O13" s="84"/>
       <c r="P13" s="86"/>
-      <c r="Q13" s="77"/>
-      <c r="R13" s="79"/>
-      <c r="S13" s="78"/>
+      <c r="Q13" s="82"/>
+      <c r="R13" s="84"/>
+      <c r="S13" s="83"/>
     </row>
     <row r="14" spans="1:19">
       <c r="A14" s="23">
         <v>12</v>
       </c>
-      <c r="B14" s="76"/>
+      <c r="B14" s="88"/>
       <c r="C14" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="77"/>
-      <c r="E14" s="77"/>
-      <c r="F14" s="77"/>
-      <c r="G14" s="77"/>
-      <c r="H14" s="77"/>
-      <c r="I14" s="77"/>
-      <c r="J14" s="77"/>
+      <c r="D14" s="82"/>
+      <c r="E14" s="82"/>
+      <c r="F14" s="82"/>
+      <c r="G14" s="82"/>
+      <c r="H14" s="82"/>
+      <c r="I14" s="82"/>
+      <c r="J14" s="82"/>
       <c r="K14" s="86"/>
       <c r="L14" s="86"/>
       <c r="M14" s="86"/>
       <c r="N14" s="86"/>
-      <c r="O14" s="79"/>
+      <c r="O14" s="84"/>
       <c r="P14" s="86"/>
-      <c r="Q14" s="77"/>
-      <c r="R14" s="79"/>
-      <c r="S14" s="78"/>
+      <c r="Q14" s="82"/>
+      <c r="R14" s="84"/>
+      <c r="S14" s="83"/>
     </row>
     <row r="15" spans="1:19">
       <c r="A15" s="24">
         <v>13</v>
       </c>
-      <c r="B15" s="76"/>
+      <c r="B15" s="88"/>
       <c r="C15" s="44"/>
-      <c r="D15" s="77"/>
-      <c r="E15" s="77"/>
-      <c r="F15" s="77"/>
-      <c r="G15" s="77"/>
-      <c r="H15" s="77"/>
-      <c r="I15" s="77"/>
-      <c r="J15" s="77"/>
+      <c r="D15" s="82"/>
+      <c r="E15" s="82"/>
+      <c r="F15" s="82"/>
+      <c r="G15" s="82"/>
+      <c r="H15" s="82"/>
+      <c r="I15" s="82"/>
+      <c r="J15" s="82"/>
       <c r="K15" s="86"/>
       <c r="L15" s="86"/>
       <c r="M15" s="86"/>
       <c r="N15" s="86"/>
-      <c r="O15" s="79"/>
+      <c r="O15" s="84"/>
       <c r="P15" s="86"/>
-      <c r="Q15" s="77"/>
-      <c r="R15" s="79"/>
-      <c r="S15" s="78"/>
+      <c r="Q15" s="82"/>
+      <c r="R15" s="84"/>
+      <c r="S15" s="83"/>
     </row>
     <row r="16" spans="1:19">
       <c r="A16" s="24">
         <v>14</v>
       </c>
-      <c r="B16" s="76"/>
+      <c r="B16" s="88"/>
       <c r="C16" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="77"/>
-      <c r="E16" s="77"/>
-      <c r="F16" s="77"/>
-      <c r="G16" s="77"/>
-      <c r="H16" s="77"/>
-      <c r="I16" s="77"/>
-      <c r="J16" s="77"/>
+      <c r="D16" s="82"/>
+      <c r="E16" s="82"/>
+      <c r="F16" s="82"/>
+      <c r="G16" s="82"/>
+      <c r="H16" s="82"/>
+      <c r="I16" s="82"/>
+      <c r="J16" s="82"/>
       <c r="K16" s="86"/>
       <c r="L16" s="86"/>
       <c r="M16" s="86"/>
       <c r="N16" s="86"/>
-      <c r="O16" s="79"/>
+      <c r="O16" s="84"/>
       <c r="P16" s="86"/>
-      <c r="Q16" s="77"/>
-      <c r="R16" s="79"/>
-      <c r="S16" s="78"/>
+      <c r="Q16" s="82"/>
+      <c r="R16" s="84"/>
+      <c r="S16" s="83"/>
     </row>
     <row r="17" spans="1:19">
       <c r="A17" s="26">
@@ -2624,11 +2624,11 @@
         <v>231</v>
       </c>
       <c r="C17" s="44"/>
-      <c r="D17" s="77"/>
-      <c r="E17" s="77"/>
-      <c r="F17" s="77"/>
-      <c r="G17" s="77"/>
-      <c r="H17" s="77"/>
+      <c r="D17" s="82"/>
+      <c r="E17" s="82"/>
+      <c r="F17" s="82"/>
+      <c r="G17" s="82"/>
+      <c r="H17" s="82"/>
       <c r="I17" s="53" t="s">
         <v>55</v>
       </c>
@@ -2639,14 +2639,27 @@
       <c r="L17" s="87"/>
       <c r="M17" s="87"/>
       <c r="N17" s="87"/>
-      <c r="O17" s="79"/>
+      <c r="O17" s="84"/>
       <c r="P17" s="87"/>
-      <c r="Q17" s="77"/>
-      <c r="R17" s="79"/>
-      <c r="S17" s="78"/>
+      <c r="Q17" s="82"/>
+      <c r="R17" s="84"/>
+      <c r="S17" s="83"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="H11:H17"/>
+    <mergeCell ref="I3:I16"/>
+    <mergeCell ref="J3:J16"/>
+    <mergeCell ref="D11:D17"/>
+    <mergeCell ref="E6:E17"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="F6:F17"/>
+    <mergeCell ref="G8:G17"/>
     <mergeCell ref="Q2:Q17"/>
     <mergeCell ref="S2:S17"/>
     <mergeCell ref="R2:R17"/>
@@ -2656,19 +2669,6 @@
     <mergeCell ref="M10:M17"/>
     <mergeCell ref="N7:N17"/>
     <mergeCell ref="P2:P17"/>
-    <mergeCell ref="H11:H17"/>
-    <mergeCell ref="I3:I16"/>
-    <mergeCell ref="J3:J16"/>
-    <mergeCell ref="D11:D17"/>
-    <mergeCell ref="E6:E17"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="F6:F17"/>
-    <mergeCell ref="G8:G17"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C2:C3"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2694,7 +2694,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="92" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
@@ -2715,7 +2715,7 @@
       <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="72" t="s">
+      <c r="I1" s="89" t="s">
         <v>0</v>
       </c>
       <c r="J1" s="11" t="s">
@@ -2738,9 +2738,11 @@
       </c>
     </row>
     <row r="2" spans="1:15">
-      <c r="A2" s="75"/>
+      <c r="A2" s="92"/>
       <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
+      <c r="C2" s="18" t="s">
+        <v>199</v>
+      </c>
       <c r="D2" s="11" t="s">
         <v>7</v>
       </c>
@@ -2753,7 +2755,7 @@
       <c r="G2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="72"/>
+      <c r="I2" s="89"/>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11" t="s">
@@ -2770,7 +2772,7 @@
       </c>
     </row>
     <row r="3" spans="1:15">
-      <c r="A3" s="75"/>
+      <c r="A3" s="92"/>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
@@ -2779,7 +2781,7 @@
         <v>11</v>
       </c>
       <c r="G3" s="11"/>
-      <c r="I3" s="72"/>
+      <c r="I3" s="89"/>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
       <c r="L3" s="11"/>
@@ -2790,14 +2792,14 @@
       <c r="O3" s="11"/>
     </row>
     <row r="4" spans="1:15">
-      <c r="A4" s="75"/>
+      <c r="A4" s="92"/>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
       <c r="G4" s="11"/>
-      <c r="I4" s="72"/>
+      <c r="I4" s="89"/>
       <c r="J4" s="11"/>
       <c r="K4" s="11"/>
       <c r="L4" s="11"/>
@@ -2909,73 +2911,73 @@
       <c r="A7" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="B7" s="73" t="s">
+      <c r="B7" s="90" t="s">
         <v>208</v>
       </c>
-      <c r="C7" s="74"/>
-      <c r="D7" s="74"/>
-      <c r="E7" s="74"/>
-      <c r="F7" s="74"/>
-      <c r="G7" s="74"/>
+      <c r="C7" s="91"/>
+      <c r="D7" s="91"/>
+      <c r="E7" s="91"/>
+      <c r="F7" s="91"/>
+      <c r="G7" s="91"/>
       <c r="I7" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="J7" s="73" t="s">
+      <c r="J7" s="90" t="s">
         <v>209</v>
       </c>
-      <c r="K7" s="74"/>
-      <c r="L7" s="74"/>
-      <c r="M7" s="74"/>
-      <c r="N7" s="74"/>
-      <c r="O7" s="74"/>
+      <c r="K7" s="91"/>
+      <c r="L7" s="91"/>
+      <c r="M7" s="91"/>
+      <c r="N7" s="91"/>
+      <c r="O7" s="91"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="14">
         <v>0</v>
       </c>
-      <c r="B8" s="72" t="s">
+      <c r="B8" s="89" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="72"/>
-      <c r="D8" s="72"/>
-      <c r="E8" s="72"/>
-      <c r="F8" s="72"/>
-      <c r="G8" s="72"/>
+      <c r="C8" s="89"/>
+      <c r="D8" s="89"/>
+      <c r="E8" s="89"/>
+      <c r="F8" s="89"/>
+      <c r="G8" s="89"/>
       <c r="I8" s="14">
         <v>0</v>
       </c>
-      <c r="J8" s="72" t="s">
+      <c r="J8" s="89" t="s">
         <v>12</v>
       </c>
-      <c r="K8" s="72"/>
-      <c r="L8" s="72"/>
-      <c r="M8" s="72"/>
-      <c r="N8" s="72"/>
-      <c r="O8" s="72"/>
+      <c r="K8" s="89"/>
+      <c r="L8" s="89"/>
+      <c r="M8" s="89"/>
+      <c r="N8" s="89"/>
+      <c r="O8" s="89"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="14">
         <v>1</v>
       </c>
-      <c r="B9" s="72" t="s">
+      <c r="B9" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="72"/>
-      <c r="D9" s="72"/>
-      <c r="E9" s="72"/>
-      <c r="F9" s="72"/>
-      <c r="G9" s="72"/>
+      <c r="C9" s="89"/>
+      <c r="D9" s="89"/>
+      <c r="E9" s="89"/>
+      <c r="F9" s="89"/>
+      <c r="G9" s="89"/>
       <c r="I9" s="14">
         <v>1</v>
       </c>
-      <c r="J9" s="72" t="s">
+      <c r="J9" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="K9" s="72"/>
-      <c r="L9" s="72"/>
-      <c r="M9" s="72"/>
-      <c r="N9" s="72"/>
-      <c r="O9" s="72"/>
+      <c r="K9" s="89"/>
+      <c r="L9" s="89"/>
+      <c r="M9" s="89"/>
+      <c r="N9" s="89"/>
+      <c r="O9" s="89"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="30">
@@ -3791,7 +3793,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="92" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
@@ -3814,7 +3816,7 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="75"/>
+      <c r="A2" s="92"/>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
       <c r="D2" s="11" t="s">
@@ -3831,7 +3833,7 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="75"/>
+      <c r="A3" s="92"/>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
@@ -3842,7 +3844,7 @@
       <c r="G3" s="11"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="75"/>
+      <c r="A4" s="92"/>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
       <c r="D4" s="11"/>
@@ -3906,40 +3908,40 @@
       <c r="A7" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="B7" s="73" t="s">
+      <c r="B7" s="90" t="s">
         <v>208</v>
       </c>
-      <c r="C7" s="74"/>
-      <c r="D7" s="74"/>
-      <c r="E7" s="74"/>
-      <c r="F7" s="74"/>
-      <c r="G7" s="74"/>
+      <c r="C7" s="91"/>
+      <c r="D7" s="91"/>
+      <c r="E7" s="91"/>
+      <c r="F7" s="91"/>
+      <c r="G7" s="91"/>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="14">
         <v>0</v>
       </c>
-      <c r="B8" s="72" t="s">
+      <c r="B8" s="89" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="72"/>
-      <c r="D8" s="72"/>
-      <c r="E8" s="72"/>
-      <c r="F8" s="72"/>
-      <c r="G8" s="72"/>
+      <c r="C8" s="89"/>
+      <c r="D8" s="89"/>
+      <c r="E8" s="89"/>
+      <c r="F8" s="89"/>
+      <c r="G8" s="89"/>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="14">
         <v>1</v>
       </c>
-      <c r="B9" s="72" t="s">
+      <c r="B9" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="72"/>
-      <c r="D9" s="72"/>
-      <c r="E9" s="72"/>
-      <c r="F9" s="72"/>
-      <c r="G9" s="72"/>
+      <c r="C9" s="89"/>
+      <c r="D9" s="89"/>
+      <c r="E9" s="89"/>
+      <c r="F9" s="89"/>
+      <c r="G9" s="89"/>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="30">
@@ -4461,19 +4463,19 @@
       <c r="A1" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="B1" s="82" t="s">
+      <c r="B1" s="95" t="s">
         <v>214</v>
       </c>
-      <c r="C1" s="83"/>
+      <c r="C1" s="96"/>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="18">
         <v>0</v>
       </c>
-      <c r="B2" s="80" t="s">
+      <c r="B2" s="93" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="81"/>
+      <c r="C2" s="94"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="32">
